--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -164,7 +164,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Notes"/>

--- a/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.DataBoundInfersWhenEnabled.verified.xlsx
@@ -145,12 +145,15 @@
       <formula>LEN(TRIM(F2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="A2:A7">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="Required field" sqref="C2:C7">
       <formula1>ISNUMBER(C2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="D2:D7">
+      <formula1>ISNUMBER(D2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="E2:E7">
       <formula1>"TRUE,FALSE"</formula1>
